--- a/Design/Excel/ET/Datas/StartConfig/StartSceneConfig.xlsx
+++ b/Design/Excel/ET/Datas/StartConfig/StartSceneConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>BenchmarkClient6</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>Admin</t>
   </si>
   <si>
     <t>Localhost</t>
@@ -1166,19 +1172,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <dimension ref="A1:H53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="3" width="12.75" style="2" customWidth="1"/>
-    <col min="4" max="5" width="12.625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="32.75" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="21.1272727272727" style="2" customWidth="1"/>
+    <col min="2" max="3" width="12.7545454545455" style="2" customWidth="1"/>
+    <col min="4" max="5" width="12.6272727272727" style="3" customWidth="1"/>
+    <col min="6" max="6" width="32.7545454545455" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.3727272727273" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.1272727272727" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" customHeight="1" spans="1:8">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1204,7 +1210,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:8">
+    <row r="2" customHeight="1" spans="1:8">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -1230,7 +1236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:8">
+    <row r="3" customHeight="1" spans="1:8">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
@@ -1256,7 +1262,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" customHeight="1" spans="1:8">
       <c r="A4" s="1"/>
       <c r="B4" s="6" t="s">
         <v>18</v>
@@ -1280,7 +1286,7 @@
         <v>10001</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" customHeight="1" spans="1:8">
       <c r="B5" s="6" t="s">
         <v>18</v>
       </c>
@@ -1301,7 +1307,7 @@
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A6" s="2"/>
       <c r="B6" s="6" t="s">
         <v>18</v>
@@ -1323,7 +1329,7 @@
       </c>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" ht="16.5" spans="1:8">
+    <row r="7" customHeight="1" spans="1:8">
       <c r="A7" s="4"/>
       <c r="B7" s="6" t="s">
         <v>18</v>
@@ -1345,7 +1351,7 @@
       </c>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" ht="16.5" spans="1:8">
+    <row r="8" customHeight="1" spans="1:8">
       <c r="A8" s="4"/>
       <c r="B8" s="6" t="s">
         <v>18</v>
@@ -1367,7 +1373,7 @@
       </c>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" ht="16.5" spans="1:8">
+    <row r="9" customHeight="1" spans="1:8">
       <c r="A9" s="4"/>
       <c r="B9" s="6" t="s">
         <v>18</v>
@@ -1389,7 +1395,7 @@
       </c>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" ht="16.5" spans="1:8">
+    <row r="10" customHeight="1" spans="1:8">
       <c r="A10" s="4"/>
       <c r="B10" s="6" t="s">
         <v>18</v>
@@ -1411,61 +1417,59 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" ht="16.5" spans="1:8">
+    <row r="11" customHeight="1" spans="1:8">
       <c r="A11" s="4"/>
       <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6">
+        <v>100001</v>
+      </c>
+      <c r="D11" s="6">
+        <v>100001</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="G11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="6">
-        <v>30002</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:8">
+        <v>27</v>
+      </c>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:8">
       <c r="A12" s="4"/>
       <c r="B12" s="6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C12" s="6">
-        <v>2</v>
+        <v>100002</v>
       </c>
       <c r="D12" s="6">
-        <v>1</v>
+        <v>100002</v>
       </c>
       <c r="E12" s="6">
         <v>1</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>30</v>
+      <c r="F12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="H12" s="6">
-        <v>30003</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:8">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:8">
       <c r="A13" s="4"/>
       <c r="B13" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" s="6">
         <v>1</v>
@@ -1473,23 +1477,23 @@
       <c r="E13" s="6">
         <v>1</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>31</v>
+      <c r="F13" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="H13" s="6">
-        <v>30004</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:8">
+        <v>30002</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="4"/>
       <c r="B14" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6">
         <v>1</v>
@@ -1498,20 +1502,22 @@
         <v>1</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:8">
+      <c r="H14" s="6">
+        <v>30003</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:8">
       <c r="A15" s="4"/>
       <c r="B15" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C15" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15" s="6">
         <v>1</v>
@@ -1520,20 +1526,22 @@
         <v>1</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:8">
+      <c r="H15" s="6">
+        <v>30004</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:8">
       <c r="A16" s="4"/>
       <c r="B16" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C16" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="6">
         <v>1</v>
@@ -1545,84 +1553,82 @@
         <v>34</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" ht="16.5" spans="1:8">
+    <row r="17" customHeight="1" spans="1:8">
       <c r="A17" s="4"/>
       <c r="B17" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C17" s="6">
+        <v>5</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:8">
+      <c r="A18" s="4"/>
+      <c r="B18" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="6">
+        <v>6</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:8">
+      <c r="A19" s="4"/>
+      <c r="B19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="6">
         <v>7</v>
       </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="D19" s="6">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="6">
+      <c r="G19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:8">
+      <c r="B20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="6">
         <v>300</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6">
-        <v>3</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" s="6">
-        <v>30300</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="2:8">
-      <c r="B19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="6">
-        <v>301</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1</v>
-      </c>
-      <c r="E19" s="6">
-        <v>3</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H19" s="6">
-        <v>30301</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="2:8">
-      <c r="B20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="6">
-        <v>302</v>
       </c>
       <c r="D20" s="6">
         <v>1</v>
@@ -1631,21 +1637,21 @@
         <v>3</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H20" s="6">
-        <v>30302</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="2:8">
+        <v>30300</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="B21" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C21" s="6">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D21" s="6">
         <v>1</v>
@@ -1654,21 +1660,21 @@
         <v>3</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>41</v>
       </c>
       <c r="H21" s="6">
-        <v>30303</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="2:8">
+        <v>30301</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="B22" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="6">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D22" s="6">
         <v>1</v>
@@ -1677,266 +1683,264 @@
         <v>3</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>42</v>
       </c>
       <c r="H22" s="6">
+        <v>30302</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="B23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="6">
+        <v>303</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>3</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" s="6">
+        <v>30303</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="B24" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="6">
+        <v>304</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6">
+        <v>3</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="6">
         <v>30304</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" spans="2:8">
-      <c r="B23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1</v>
-      </c>
-      <c r="F23" s="6" t="s">
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="B25" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="6">
+        <v>100001</v>
+      </c>
+      <c r="D25" s="6">
+        <v>100001</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="B26" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="6">
+        <v>100002</v>
+      </c>
+      <c r="D26" s="6">
+        <v>100002</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G26" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H26" s="6">
+        <v>31002</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="B27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="6">
+        <v>1</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" s="6">
         <v>30002</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" spans="2:8">
-      <c r="B24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="6">
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="B28" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="6">
         <v>2</v>
       </c>
-      <c r="D24" s="6">
-        <v>1</v>
-      </c>
-      <c r="E24" s="6">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="6">
+      <c r="D28" s="6">
+        <v>1</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="6">
         <v>30003</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" spans="2:8">
-      <c r="B25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="6">
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="B29" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="6">
         <v>3</v>
       </c>
-      <c r="D25" s="6">
-        <v>1</v>
-      </c>
-      <c r="E25" s="6">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="D29" s="6">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="6">
+      <c r="G29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29" s="6">
         <v>30004</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" spans="2:8">
-      <c r="B26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="6">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="B30" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="6">
         <v>4</v>
       </c>
-      <c r="D26" s="6">
-        <v>1</v>
-      </c>
-      <c r="E26" s="6">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="2:8">
-      <c r="B27" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="D30" s="6">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="B31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="6">
         <v>5</v>
       </c>
-      <c r="D27" s="6">
-        <v>1</v>
-      </c>
-      <c r="E27" s="6">
-        <v>1</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="2:8">
-      <c r="B28" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="6">
+      <c r="D31" s="6">
+        <v>1</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="B32" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="6">
         <v>6</v>
       </c>
-      <c r="D28" s="6">
-        <v>1</v>
-      </c>
-      <c r="E28" s="6">
-        <v>1</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H28" s="6"/>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="2:8">
-      <c r="B29" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="6">
+      <c r="D32" s="6">
+        <v>1</v>
+      </c>
+      <c r="E32" s="6">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B33" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="6">
         <v>7</v>
       </c>
-      <c r="D29" s="6">
-        <v>1</v>
-      </c>
-      <c r="E29" s="6">
-        <v>1</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="D33" s="6">
+        <v>1</v>
+      </c>
+      <c r="E33" s="6">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="2:8">
-      <c r="B30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="6">
+      <c r="G33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="6">
         <v>300</v>
-      </c>
-      <c r="D30" s="6">
-        <v>1</v>
-      </c>
-      <c r="E30" s="6">
-        <v>3</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H30" s="6">
-        <v>30300</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="2:8">
-      <c r="B31" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="6">
-        <v>301</v>
-      </c>
-      <c r="D31" s="6">
-        <v>1</v>
-      </c>
-      <c r="E31" s="6">
-        <v>3</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H31" s="6">
-        <v>30301</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="2:8">
-      <c r="B32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="6">
-        <v>302</v>
-      </c>
-      <c r="D32" s="6">
-        <v>1</v>
-      </c>
-      <c r="E32" s="6">
-        <v>3</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H32" s="6">
-        <v>30302</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="2:8">
-      <c r="B33" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="6">
-        <v>303</v>
-      </c>
-      <c r="D33" s="6">
-        <v>1</v>
-      </c>
-      <c r="E33" s="6">
-        <v>3</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H33" s="6">
-        <v>30303</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="2:8">
-      <c r="B34" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="6">
-        <v>304</v>
       </c>
       <c r="D34" s="6">
         <v>1</v>
@@ -1945,260 +1949,440 @@
         <v>3</v>
       </c>
       <c r="F34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H34" s="6">
+        <v>30300</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="6">
+        <v>301</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1</v>
+      </c>
+      <c r="E35" s="6">
+        <v>3</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H35" s="6">
+        <v>30301</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="6">
+        <v>302</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1</v>
+      </c>
+      <c r="E36" s="6">
+        <v>3</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36" s="6">
+        <v>30302</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B37" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="6">
+        <v>303</v>
+      </c>
+      <c r="D37" s="6">
+        <v>1</v>
+      </c>
+      <c r="E37" s="6">
+        <v>3</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H37" s="6">
+        <v>30303</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B38" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="6">
+        <v>304</v>
+      </c>
+      <c r="D38" s="6">
+        <v>1</v>
+      </c>
+      <c r="E38" s="6">
+        <v>3</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H38" s="6">
+        <v>30304</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B39" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="6">
+        <v>100001</v>
+      </c>
+      <c r="D39" s="6">
+        <v>100001</v>
+      </c>
+      <c r="E39" s="6">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B40" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="6">
+        <v>100002</v>
+      </c>
+      <c r="D40" s="6">
+        <v>100002</v>
+      </c>
+      <c r="E40" s="6">
+        <v>1</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="6">
+        <v>31002</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B41" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="6">
+        <v>1</v>
+      </c>
+      <c r="D41" s="6">
+        <v>1</v>
+      </c>
+      <c r="E41" s="6">
+        <v>1</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H41" s="6">
+        <v>30002</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B42" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="6">
+        <v>2</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1</v>
+      </c>
+      <c r="E42" s="6">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H42" s="6">
+        <v>30003</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B43" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="6">
+        <v>3</v>
+      </c>
+      <c r="D43" s="6">
+        <v>1</v>
+      </c>
+      <c r="E43" s="6">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H43" s="6">
+        <v>30004</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B44" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="6">
+        <v>4</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1</v>
+      </c>
+      <c r="E44" s="6">
+        <v>1</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B45" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="6">
+        <v>5</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1</v>
+      </c>
+      <c r="E45" s="6">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B46" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="6">
+        <v>6</v>
+      </c>
+      <c r="D46" s="6">
+        <v>1</v>
+      </c>
+      <c r="E46" s="6">
+        <v>1</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B47" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="6">
+        <v>400</v>
+      </c>
+      <c r="D47" s="6">
+        <v>3</v>
+      </c>
+      <c r="E47" s="6">
+        <v>3</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H47" s="6">
+        <v>30300</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B48" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="6">
+        <v>401</v>
+      </c>
+      <c r="D48" s="6">
+        <v>4</v>
+      </c>
+      <c r="E48" s="6">
+        <v>3</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H48" s="6">
+        <v>30301</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B49" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="6">
+        <v>402</v>
+      </c>
+      <c r="D49" s="6">
+        <v>5</v>
+      </c>
+      <c r="E49" s="6">
+        <v>3</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G49" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H49" s="6">
+        <v>30302</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B50" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="6">
+        <v>403</v>
+      </c>
+      <c r="D50" s="6">
+        <v>6</v>
+      </c>
+      <c r="E50" s="6">
+        <v>3</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H50" s="6">
+        <v>30303</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="2:8">
+      <c r="B51" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="6">
+        <v>404</v>
+      </c>
+      <c r="D51" s="6">
+        <v>7</v>
+      </c>
+      <c r="E51" s="6">
+        <v>3</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H51" s="6">
         <v>30304</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" spans="2:8">
-      <c r="B35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1</v>
-      </c>
-      <c r="E35" s="6">
-        <v>1</v>
-      </c>
-      <c r="F35" s="6" t="s">
+    <row r="52" customHeight="1" spans="2:8">
+      <c r="B52" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="6">
+        <v>100001</v>
+      </c>
+      <c r="D52" s="6">
+        <v>100001</v>
+      </c>
+      <c r="E52" s="6">
+        <v>1</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" customHeight="1" spans="2:8">
+      <c r="B53" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="6">
+        <v>100002</v>
+      </c>
+      <c r="D53" s="6">
+        <v>100002</v>
+      </c>
+      <c r="E53" s="6">
+        <v>1</v>
+      </c>
+      <c r="F53" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G53" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H35" s="6">
-        <v>30002</v>
-      </c>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="2:8">
-      <c r="B36" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1</v>
-      </c>
-      <c r="E36" s="6">
-        <v>1</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H36" s="6">
-        <v>30003</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" spans="2:8">
-      <c r="B37" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C37" s="6">
-        <v>3</v>
-      </c>
-      <c r="D37" s="6">
-        <v>1</v>
-      </c>
-      <c r="E37" s="6">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H37" s="6">
-        <v>30004</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" spans="2:8">
-      <c r="B38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="6">
-        <v>4</v>
-      </c>
-      <c r="D38" s="6">
-        <v>1</v>
-      </c>
-      <c r="E38" s="6">
-        <v>1</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H38" s="6"/>
-    </row>
-    <row r="39" s="2" customFormat="1" spans="2:8">
-      <c r="B39" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="6">
-        <v>5</v>
-      </c>
-      <c r="D39" s="6">
-        <v>1</v>
-      </c>
-      <c r="E39" s="6">
-        <v>1</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H39" s="6"/>
-    </row>
-    <row r="40" s="2" customFormat="1" spans="2:8">
-      <c r="B40" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="6">
-        <v>6</v>
-      </c>
-      <c r="D40" s="6">
-        <v>1</v>
-      </c>
-      <c r="E40" s="6">
-        <v>1</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H40" s="6"/>
-    </row>
-    <row r="41" s="2" customFormat="1" spans="2:8">
-      <c r="B41" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="6">
-        <v>400</v>
-      </c>
-      <c r="D41" s="6">
-        <v>3</v>
-      </c>
-      <c r="E41" s="6">
-        <v>3</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H41" s="6">
-        <v>30300</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" spans="2:8">
-      <c r="B42" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" s="6">
-        <v>401</v>
-      </c>
-      <c r="D42" s="6">
-        <v>4</v>
-      </c>
-      <c r="E42" s="6">
-        <v>3</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H42" s="6">
-        <v>30301</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" spans="2:8">
-      <c r="B43" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="6">
-        <v>402</v>
-      </c>
-      <c r="D43" s="6">
-        <v>5</v>
-      </c>
-      <c r="E43" s="6">
-        <v>3</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H43" s="6">
-        <v>30302</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" spans="2:8">
-      <c r="B44" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44" s="6">
-        <v>403</v>
-      </c>
-      <c r="D44" s="6">
-        <v>6</v>
-      </c>
-      <c r="E44" s="6">
-        <v>3</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H44" s="6">
-        <v>30303</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" spans="2:8">
-      <c r="B45" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C45" s="6">
-        <v>404</v>
-      </c>
-      <c r="D45" s="6">
-        <v>7</v>
-      </c>
-      <c r="E45" s="6">
-        <v>3</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H45" s="6">
-        <v>30304</v>
+      <c r="H53" s="6">
+        <v>31002</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/StartConfig/StartSceneConfig.xlsx
+++ b/Design/Excel/ET/Datas/StartConfig/StartSceneConfig.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Work\GameDevelopmentKit_Demo\Design\Excel\ET\Datas\StartConfig\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView windowHeight="17200"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0" fullPrecision="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -168,6 +173,9 @@
   </si>
   <si>
     <t>RouterTest</t>
+  </si>
+  <si>
+    <t>SurvivorRoomManager</t>
   </si>
 </sst>
 </file>
@@ -180,7 +188,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,7 +220,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -220,14 +228,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -243,7 +251,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -274,7 +282,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -282,7 +290,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -290,7 +298,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -298,14 +306,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -313,42 +321,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -660,149 +661,149 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1172,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="21.1272727272727" style="2" customWidth="1"/>
@@ -2385,9 +2386,72 @@
         <v>31002</v>
       </c>
     </row>
+    <row r="54" ht="14" spans="2:8">
+      <c r="B54" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54" s="6">
+        <v>8</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1</v>
+      </c>
+      <c r="E54" s="6">
+        <v>1</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" ht="14" spans="2:8">
+      <c r="B55" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C55" s="6">
+        <v>8</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1</v>
+      </c>
+      <c r="E55" s="6">
+        <v>1</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" ht="14" spans="2:8">
+      <c r="B56" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="6">
+        <v>8</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1</v>
+      </c>
+      <c r="E56" s="6">
+        <v>1</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H56" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>